--- a/data/answer_sheet.xlsx
+++ b/data/answer_sheet.xlsx
@@ -75,7 +75,7 @@
     <t>预期原因</t>
   </si>
   <si>
-    <t>错误发票_税额错误</t>
+    <t>error_tax_amount</t>
   </si>
   <si>
     <t>110102345678</t>
@@ -93,10 +93,10 @@
     <t>异常</t>
   </si>
   <si>
-    <t>税额≠金额×税率</t>
-  </si>
-  <si>
-    <t>错误发票_号码重复</t>
+    <t>税额不符</t>
+  </si>
+  <si>
+    <t>error_duplicate</t>
   </si>
   <si>
     <t>1100143160</t>
@@ -111,10 +111,10 @@
     <t>91120116MA7D9H2R3U</t>
   </si>
   <si>
-    <t>号码和正常发票1重复</t>
-  </si>
-  <si>
-    <t>错误发票_价税合计</t>
+    <t>号码重复</t>
+  </si>
+  <si>
+    <t>error_total</t>
   </si>
   <si>
     <t>2024060201</t>
@@ -126,10 +126,10 @@
     <t>91310115MA7654321X</t>
   </si>
   <si>
-    <t>价税合计≠金额+税额</t>
-  </si>
-  <si>
-    <t>错误发票_税率错误</t>
+    <t>价税合计不符</t>
+  </si>
+  <si>
+    <t>error_tax_rate</t>
   </si>
   <si>
     <t>2024060202</t>
@@ -141,10 +141,10 @@
     <t>91320594MA7D3C8P1K</t>
   </si>
   <si>
-    <t>税率填13%以外的非法值</t>
-  </si>
-  <si>
-    <t>正常发票_旋转阴影</t>
+    <t>税率非法</t>
+  </si>
+  <si>
+    <t>normal_rotated</t>
   </si>
   <si>
     <t>01234576</t>
@@ -159,7 +159,7 @@
     <t>通过</t>
   </si>
   <si>
-    <t>正常发票1</t>
+    <t>normal_1</t>
   </si>
   <si>
     <t>上海远景办公设备有限公司</t>
@@ -168,7 +168,7 @@
     <t>91310115MA1F2G3H4J</t>
   </si>
   <si>
-    <t>正常发票2</t>
+    <t>normal_2</t>
   </si>
   <si>
     <t>1100143168</t>
@@ -183,7 +183,7 @@
     <t>91110108MA0B7C8D9E</t>
   </si>
   <si>
-    <t>正常发票3</t>
+    <t>normal_3</t>
   </si>
   <si>
     <t>1100143161</t>
@@ -198,7 +198,7 @@
     <t>91320594MA3Q7B2L8K</t>
   </si>
   <si>
-    <t>正常发票4</t>
+    <t>normal_4</t>
   </si>
   <si>
     <t>1100143162</t>
@@ -207,7 +207,7 @@
     <t>01234569</t>
   </si>
   <si>
-    <t>正常发票5</t>
+    <t>normal_5</t>
   </si>
   <si>
     <t>1100143163</t>
@@ -222,7 +222,7 @@
     <t>91440101MA5CL8D27H</t>
   </si>
   <si>
-    <t>正常发票6</t>
+    <t>normal_6</t>
   </si>
   <si>
     <t>1100143164</t>
@@ -237,7 +237,7 @@
     <t>91440300MA5K1L2M3N</t>
   </si>
   <si>
-    <t>正常发票7</t>
+    <t>normal_7</t>
   </si>
   <si>
     <t>1100143165</t>
@@ -252,7 +252,7 @@
     <t>91120116MA06P3K9H2</t>
   </si>
   <si>
-    <t>正常发票8</t>
+    <t>normal_8</t>
   </si>
   <si>
     <t>1100143166</t>
@@ -267,7 +267,7 @@
     <t>91330109MA2B1C3D4E</t>
   </si>
   <si>
-    <t>正常发票9</t>
+    <t>normal_9</t>
   </si>
   <si>
     <t>1100143167</t>
@@ -282,7 +282,7 @@
     <t>91330212MA2J5K6L7M</t>
   </si>
   <si>
-    <t>正常发票10</t>
+    <t>normal_10</t>
   </si>
   <si>
     <t>北京华创办公设备有限公司</t>
@@ -1438,7 +1438,7 @@
       <c r="L4" t="s">
         <v>18</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       <c r="L5" t="s">
         <v>18</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L6 L7:L16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L16">
       <formula1>"通过,异常"</formula1>
     </dataValidation>
   </dataValidations>
